--- a/code/resultados/NWJSSP_OADG_NEH(BestImprovement_LocalSearch).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(BestImprovement_LocalSearch).xlsx
@@ -13,6 +13,12 @@
     <sheet name="ft10r" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ft20" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j100_m10_1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,29 +434,1291 @@
       <c r="B1" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47</v>
+      </c>
+      <c r="E2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6699109</v>
+      </c>
+      <c r="B1" t="n">
+        <v>29217</v>
+      </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr"/>
       <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
+      <c r="AW1" t="inlineStr"/>
+      <c r="AX1" t="inlineStr"/>
+      <c r="AY1" t="inlineStr"/>
+      <c r="AZ1" t="inlineStr"/>
+      <c r="BA1" t="inlineStr"/>
+      <c r="BB1" t="inlineStr"/>
+      <c r="BC1" t="inlineStr"/>
+      <c r="BD1" t="inlineStr"/>
+      <c r="BE1" t="inlineStr"/>
+      <c r="BF1" t="inlineStr"/>
+      <c r="BG1" t="inlineStr"/>
+      <c r="BH1" t="inlineStr"/>
+      <c r="BI1" t="inlineStr"/>
+      <c r="BJ1" t="inlineStr"/>
+      <c r="BK1" t="inlineStr"/>
+      <c r="BL1" t="inlineStr"/>
+      <c r="BM1" t="inlineStr"/>
+      <c r="BN1" t="inlineStr"/>
+      <c r="BO1" t="inlineStr"/>
+      <c r="BP1" t="inlineStr"/>
+      <c r="BQ1" t="inlineStr"/>
+      <c r="BR1" t="inlineStr"/>
+      <c r="BS1" t="inlineStr"/>
+      <c r="BT1" t="inlineStr"/>
+      <c r="BU1" t="inlineStr"/>
+      <c r="BV1" t="inlineStr"/>
+      <c r="BW1" t="inlineStr"/>
+      <c r="BX1" t="inlineStr"/>
+      <c r="BY1" t="inlineStr"/>
+      <c r="BZ1" t="inlineStr"/>
+      <c r="CA1" t="inlineStr"/>
+      <c r="CB1" t="inlineStr"/>
+      <c r="CC1" t="inlineStr"/>
+      <c r="CD1" t="inlineStr"/>
+      <c r="CE1" t="inlineStr"/>
+      <c r="CF1" t="inlineStr"/>
+      <c r="CG1" t="inlineStr"/>
+      <c r="CH1" t="inlineStr"/>
+      <c r="CI1" t="inlineStr"/>
+      <c r="CJ1" t="inlineStr"/>
+      <c r="CK1" t="inlineStr"/>
+      <c r="CL1" t="inlineStr"/>
+      <c r="CM1" t="inlineStr"/>
+      <c r="CN1" t="inlineStr"/>
+      <c r="CO1" t="inlineStr"/>
+      <c r="CP1" t="inlineStr"/>
+      <c r="CQ1" t="inlineStr"/>
+      <c r="CR1" t="inlineStr"/>
+      <c r="CS1" t="inlineStr"/>
+      <c r="CT1" t="inlineStr"/>
+      <c r="CU1" t="inlineStr"/>
+      <c r="CV1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>56191</v>
+      </c>
+      <c r="B2" t="n">
+        <v>50355</v>
+      </c>
+      <c r="C2" t="n">
+        <v>64473</v>
+      </c>
+      <c r="D2" t="n">
+        <v>103829</v>
+      </c>
+      <c r="E2" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46715</v>
+      </c>
+      <c r="G2" t="n">
+        <v>66747</v>
+      </c>
+      <c r="H2" t="n">
+        <v>92103</v>
+      </c>
+      <c r="I2" t="n">
+        <v>110821</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1555</v>
+      </c>
+      <c r="K2" t="n">
+        <v>36390</v>
+      </c>
+      <c r="L2" t="n">
+        <v>72441</v>
+      </c>
+      <c r="M2" t="n">
+        <v>13905</v>
+      </c>
+      <c r="N2" t="n">
+        <v>69175</v>
+      </c>
+      <c r="O2" t="n">
+        <v>47442</v>
+      </c>
+      <c r="P2" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>52993</v>
+      </c>
+      <c r="R2" t="n">
+        <v>52458</v>
+      </c>
+      <c r="S2" t="n">
+        <v>42721</v>
+      </c>
+      <c r="T2" t="n">
+        <v>35537</v>
+      </c>
+      <c r="U2" t="n">
+        <v>129905</v>
+      </c>
+      <c r="V2" t="n">
+        <v>126905</v>
+      </c>
+      <c r="W2" t="n">
+        <v>93144</v>
+      </c>
+      <c r="X2" t="n">
+        <v>104412</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>125231</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>19781</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>40237</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>67205</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>13031</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>52418</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>17540</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>116805</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>114720</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>59527</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>32103</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>96030</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>76357</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>93907</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>112449</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>74462</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>8626</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>25961</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>132666</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>122261</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>47407</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>71279</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8958</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>87958</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>97276</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>57385</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>132758</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>26545</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>81024</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>38491</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>19091</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>30613</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>9907</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>109635</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>41633</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>39837</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>34216</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>2741</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>26124</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>72271</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>97960</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>83267</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>14426</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>106323</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>90418</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>23137</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>59300</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>90644</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5225</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>67086</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>83719</v>
+      </c>
+      <c r="BX2" t="n">
         <v>0</v>
       </c>
+      <c r="BY2" t="n">
+        <v>87625</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>23553</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>124943</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>61555</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>120280</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>28275</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>35676</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>87907</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>17310</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>78939</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>12049</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>7233</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>76555</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>118016</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>82563</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>755</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>4778</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>55890</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>31662</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>109060</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>115424</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>62445</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>99101</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>21769</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>43964871</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3634086</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
+      <c r="AW1" t="inlineStr"/>
+      <c r="AX1" t="inlineStr"/>
+      <c r="AY1" t="inlineStr"/>
+      <c r="AZ1" t="inlineStr"/>
+      <c r="BA1" t="inlineStr"/>
+      <c r="BB1" t="inlineStr"/>
+      <c r="BC1" t="inlineStr"/>
+      <c r="BD1" t="inlineStr"/>
+      <c r="BE1" t="inlineStr"/>
+      <c r="BF1" t="inlineStr"/>
+      <c r="BG1" t="inlineStr"/>
+      <c r="BH1" t="inlineStr"/>
+      <c r="BI1" t="inlineStr"/>
+      <c r="BJ1" t="inlineStr"/>
+      <c r="BK1" t="inlineStr"/>
+      <c r="BL1" t="inlineStr"/>
+      <c r="BM1" t="inlineStr"/>
+      <c r="BN1" t="inlineStr"/>
+      <c r="BO1" t="inlineStr"/>
+      <c r="BP1" t="inlineStr"/>
+      <c r="BQ1" t="inlineStr"/>
+      <c r="BR1" t="inlineStr"/>
+      <c r="BS1" t="inlineStr"/>
+      <c r="BT1" t="inlineStr"/>
+      <c r="BU1" t="inlineStr"/>
+      <c r="BV1" t="inlineStr"/>
+      <c r="BW1" t="inlineStr"/>
+      <c r="BX1" t="inlineStr"/>
+      <c r="BY1" t="inlineStr"/>
+      <c r="BZ1" t="inlineStr"/>
+      <c r="CA1" t="inlineStr"/>
+      <c r="CB1" t="inlineStr"/>
+      <c r="CC1" t="inlineStr"/>
+      <c r="CD1" t="inlineStr"/>
+      <c r="CE1" t="inlineStr"/>
+      <c r="CF1" t="inlineStr"/>
+      <c r="CG1" t="inlineStr"/>
+      <c r="CH1" t="inlineStr"/>
+      <c r="CI1" t="inlineStr"/>
+      <c r="CJ1" t="inlineStr"/>
+      <c r="CK1" t="inlineStr"/>
+      <c r="CL1" t="inlineStr"/>
+      <c r="CM1" t="inlineStr"/>
+      <c r="CN1" t="inlineStr"/>
+      <c r="CO1" t="inlineStr"/>
+      <c r="CP1" t="inlineStr"/>
+      <c r="CQ1" t="inlineStr"/>
+      <c r="CR1" t="inlineStr"/>
+      <c r="CS1" t="inlineStr"/>
+      <c r="CT1" t="inlineStr"/>
+      <c r="CU1" t="inlineStr"/>
+      <c r="CV1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>101430</v>
+      </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>374520</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>330</v>
       </c>
       <c r="D2" t="n">
-        <v>47</v>
+        <v>758982</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>427468</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>579857</v>
+      </c>
+      <c r="G2" t="n">
+        <v>366221</v>
+      </c>
+      <c r="H2" t="n">
+        <v>212098</v>
+      </c>
+      <c r="I2" t="n">
+        <v>232395</v>
+      </c>
+      <c r="J2" t="n">
+        <v>190548</v>
+      </c>
+      <c r="K2" t="n">
+        <v>798254</v>
+      </c>
+      <c r="L2" t="n">
+        <v>423173</v>
+      </c>
+      <c r="M2" t="n">
+        <v>384051</v>
+      </c>
+      <c r="N2" t="n">
+        <v>597282</v>
+      </c>
+      <c r="O2" t="n">
+        <v>248345</v>
+      </c>
+      <c r="P2" t="n">
+        <v>63875</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>112740</v>
+      </c>
+      <c r="R2" t="n">
+        <v>142804</v>
+      </c>
+      <c r="S2" t="n">
+        <v>326243</v>
+      </c>
+      <c r="T2" t="n">
+        <v>649076</v>
+      </c>
+      <c r="U2" t="n">
+        <v>260345</v>
+      </c>
+      <c r="V2" t="n">
+        <v>630082</v>
+      </c>
+      <c r="W2" t="n">
+        <v>725889</v>
+      </c>
+      <c r="X2" t="n">
+        <v>473358</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>65931</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>684244</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>830174</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>182319</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>568579</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>693136</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>512666</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>332816</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>611307</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>341653</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>309441</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>533107</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>162161</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>317873</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>30640</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>458902</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>50884</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>327621</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>121335</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>197784</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>728999</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>12345</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>672324</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>489853</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>16245</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>411977</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>350588</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>443407</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>133504</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>272997</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>806901</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>589295</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>92292</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>686450</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>515671</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>30453</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>212969</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>776703</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>8908</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>288978</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>129712</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>770362</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>616661</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>418923</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>249807</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>163688</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>211522</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>405344</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>639868</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>515926</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>697667</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>729187</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>364709</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>824868</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>547181</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>43792</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>650718</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>638594</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>172621</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>327562</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>387306</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>546594</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>115228</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>74618</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>238307</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>590990</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>551678</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>75433</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>85589</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>736096</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>461882</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>281012</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>785178</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>505496</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>459286</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>44930851</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3616924</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
+      <c r="AW1" t="inlineStr"/>
+      <c r="AX1" t="inlineStr"/>
+      <c r="AY1" t="inlineStr"/>
+      <c r="AZ1" t="inlineStr"/>
+      <c r="BA1" t="inlineStr"/>
+      <c r="BB1" t="inlineStr"/>
+      <c r="BC1" t="inlineStr"/>
+      <c r="BD1" t="inlineStr"/>
+      <c r="BE1" t="inlineStr"/>
+      <c r="BF1" t="inlineStr"/>
+      <c r="BG1" t="inlineStr"/>
+      <c r="BH1" t="inlineStr"/>
+      <c r="BI1" t="inlineStr"/>
+      <c r="BJ1" t="inlineStr"/>
+      <c r="BK1" t="inlineStr"/>
+      <c r="BL1" t="inlineStr"/>
+      <c r="BM1" t="inlineStr"/>
+      <c r="BN1" t="inlineStr"/>
+      <c r="BO1" t="inlineStr"/>
+      <c r="BP1" t="inlineStr"/>
+      <c r="BQ1" t="inlineStr"/>
+      <c r="BR1" t="inlineStr"/>
+      <c r="BS1" t="inlineStr"/>
+      <c r="BT1" t="inlineStr"/>
+      <c r="BU1" t="inlineStr"/>
+      <c r="BV1" t="inlineStr"/>
+      <c r="BW1" t="inlineStr"/>
+      <c r="BX1" t="inlineStr"/>
+      <c r="BY1" t="inlineStr"/>
+      <c r="BZ1" t="inlineStr"/>
+      <c r="CA1" t="inlineStr"/>
+      <c r="CB1" t="inlineStr"/>
+      <c r="CC1" t="inlineStr"/>
+      <c r="CD1" t="inlineStr"/>
+      <c r="CE1" t="inlineStr"/>
+      <c r="CF1" t="inlineStr"/>
+      <c r="CG1" t="inlineStr"/>
+      <c r="CH1" t="inlineStr"/>
+      <c r="CI1" t="inlineStr"/>
+      <c r="CJ1" t="inlineStr"/>
+      <c r="CK1" t="inlineStr"/>
+      <c r="CL1" t="inlineStr"/>
+      <c r="CM1" t="inlineStr"/>
+      <c r="CN1" t="inlineStr"/>
+      <c r="CO1" t="inlineStr"/>
+      <c r="CP1" t="inlineStr"/>
+      <c r="CQ1" t="inlineStr"/>
+      <c r="CR1" t="inlineStr"/>
+      <c r="CS1" t="inlineStr"/>
+      <c r="CT1" t="inlineStr"/>
+      <c r="CU1" t="inlineStr"/>
+      <c r="CV1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>108714</v>
+      </c>
+      <c r="B2" t="n">
+        <v>735622</v>
+      </c>
+      <c r="C2" t="n">
+        <v>505866</v>
+      </c>
+      <c r="D2" t="n">
+        <v>184968</v>
+      </c>
+      <c r="E2" t="n">
+        <v>280669</v>
+      </c>
+      <c r="F2" t="n">
+        <v>445991</v>
+      </c>
+      <c r="G2" t="n">
+        <v>554558</v>
+      </c>
+      <c r="H2" t="n">
+        <v>412596</v>
+      </c>
+      <c r="I2" t="n">
+        <v>142980</v>
+      </c>
+      <c r="J2" t="n">
+        <v>301435</v>
+      </c>
+      <c r="K2" t="n">
+        <v>803843</v>
+      </c>
+      <c r="L2" t="n">
+        <v>383172</v>
+      </c>
+      <c r="M2" t="n">
+        <v>471696</v>
+      </c>
+      <c r="N2" t="n">
+        <v>822519</v>
+      </c>
+      <c r="O2" t="n">
+        <v>781126</v>
+      </c>
+      <c r="P2" t="n">
+        <v>595684</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>353574</v>
+      </c>
+      <c r="R2" t="n">
+        <v>79905</v>
+      </c>
+      <c r="S2" t="n">
+        <v>687418</v>
+      </c>
+      <c r="T2" t="n">
+        <v>40931</v>
+      </c>
+      <c r="U2" t="n">
+        <v>63396</v>
+      </c>
+      <c r="V2" t="n">
+        <v>786443</v>
+      </c>
+      <c r="W2" t="n">
+        <v>349981</v>
+      </c>
+      <c r="X2" t="n">
+        <v>287552</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>589151</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>76683</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>652435</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>513097</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>807396</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>745093</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>264752</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>462287</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>705841</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2995</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>433764</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>352314</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>45417</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>403936</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>293459</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>620067</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4451</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>465353</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>330660</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>362786</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6848</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>40526</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>698023</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>159861</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>94140</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>690933</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>567517</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>308210</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>497424</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>707591</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>217575</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>33561</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>722430</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>214466</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>567213</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>414919</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>429098</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>406707</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>220852</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>134817</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>359790</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1785</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>189185</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>544459</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>662673</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>113740</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>121965</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>698861</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>256289</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>835460</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>610128</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>40521</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>125207</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>173036</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>528667</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>173477</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>398026</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>625250</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>532762</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>246338</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>308987</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>50052</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>271299</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>654387</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>645009</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>493504</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>322083</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>232078</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>755742</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>558311</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>770454</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>468683</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>580419</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>501962</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>636307</v>
       </c>
     </row>
   </sheetData>
@@ -474,10 +1742,6 @@
       <c r="B1" t="n">
         <v>0</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -520,14 +1784,6 @@
       <c r="B1" t="n">
         <v>4</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -582,14 +1838,6 @@
       <c r="B1" t="n">
         <v>5</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -644,6 +1892,298 @@
       <c r="B1" t="n">
         <v>33</v>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B2" t="n">
+        <v>409</v>
+      </c>
+      <c r="C2" t="n">
+        <v>690</v>
+      </c>
+      <c r="D2" t="n">
+        <v>781</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1490</v>
+      </c>
+      <c r="G2" t="n">
+        <v>644</v>
+      </c>
+      <c r="H2" t="n">
+        <v>205</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1553</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1121</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1649</v>
+      </c>
+      <c r="L2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1331</v>
+      </c>
+      <c r="N2" t="n">
+        <v>370</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1021</v>
+      </c>
+      <c r="P2" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>118</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1120</v>
+      </c>
+      <c r="S2" t="n">
+        <v>958</v>
+      </c>
+      <c r="T2" t="n">
+        <v>622</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>20908</v>
+      </c>
+      <c r="B1" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1332</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1173</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1057</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1754</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1767</v>
+      </c>
+      <c r="H2" t="n">
+        <v>433</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1443</v>
+      </c>
+      <c r="J2" t="n">
+        <v>170</v>
+      </c>
+      <c r="K2" t="n">
+        <v>660</v>
+      </c>
+      <c r="L2" t="n">
+        <v>531</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1595</v>
+      </c>
+      <c r="N2" t="n">
+        <v>316</v>
+      </c>
+      <c r="O2" t="n">
+        <v>955</v>
+      </c>
+      <c r="P2" t="n">
+        <v>959</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>791</v>
+      </c>
+      <c r="R2" t="n">
+        <v>681</v>
+      </c>
+      <c r="S2" t="n">
+        <v>101</v>
+      </c>
+      <c r="T2" t="n">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>119500</v>
+      </c>
+      <c r="B1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>235</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10068</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12493</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3058</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4593</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7954</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13721</v>
+      </c>
+      <c r="I2" t="n">
+        <v>9499</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>114667</v>
+      </c>
+      <c r="B1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>12735</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2031</v>
+      </c>
+      <c r="C2" t="n">
+        <v>957</v>
+      </c>
+      <c r="D2" t="n">
+        <v>13958</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7771</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4623</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7763</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10148</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6998901</v>
+      </c>
+      <c r="B1" t="n">
+        <v>18556</v>
+      </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr"/>
@@ -662,169 +2202,387 @@
       <c r="R1" t="inlineStr"/>
       <c r="S1" t="inlineStr"/>
       <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
+      <c r="AW1" t="inlineStr"/>
+      <c r="AX1" t="inlineStr"/>
+      <c r="AY1" t="inlineStr"/>
+      <c r="AZ1" t="inlineStr"/>
+      <c r="BA1" t="inlineStr"/>
+      <c r="BB1" t="inlineStr"/>
+      <c r="BC1" t="inlineStr"/>
+      <c r="BD1" t="inlineStr"/>
+      <c r="BE1" t="inlineStr"/>
+      <c r="BF1" t="inlineStr"/>
+      <c r="BG1" t="inlineStr"/>
+      <c r="BH1" t="inlineStr"/>
+      <c r="BI1" t="inlineStr"/>
+      <c r="BJ1" t="inlineStr"/>
+      <c r="BK1" t="inlineStr"/>
+      <c r="BL1" t="inlineStr"/>
+      <c r="BM1" t="inlineStr"/>
+      <c r="BN1" t="inlineStr"/>
+      <c r="BO1" t="inlineStr"/>
+      <c r="BP1" t="inlineStr"/>
+      <c r="BQ1" t="inlineStr"/>
+      <c r="BR1" t="inlineStr"/>
+      <c r="BS1" t="inlineStr"/>
+      <c r="BT1" t="inlineStr"/>
+      <c r="BU1" t="inlineStr"/>
+      <c r="BV1" t="inlineStr"/>
+      <c r="BW1" t="inlineStr"/>
+      <c r="BX1" t="inlineStr"/>
+      <c r="BY1" t="inlineStr"/>
+      <c r="BZ1" t="inlineStr"/>
+      <c r="CA1" t="inlineStr"/>
+      <c r="CB1" t="inlineStr"/>
+      <c r="CC1" t="inlineStr"/>
+      <c r="CD1" t="inlineStr"/>
+      <c r="CE1" t="inlineStr"/>
+      <c r="CF1" t="inlineStr"/>
+      <c r="CG1" t="inlineStr"/>
+      <c r="CH1" t="inlineStr"/>
+      <c r="CI1" t="inlineStr"/>
+      <c r="CJ1" t="inlineStr"/>
+      <c r="CK1" t="inlineStr"/>
+      <c r="CL1" t="inlineStr"/>
+      <c r="CM1" t="inlineStr"/>
+      <c r="CN1" t="inlineStr"/>
+      <c r="CO1" t="inlineStr"/>
+      <c r="CP1" t="inlineStr"/>
+      <c r="CQ1" t="inlineStr"/>
+      <c r="CR1" t="inlineStr"/>
+      <c r="CS1" t="inlineStr"/>
+      <c r="CT1" t="inlineStr"/>
+      <c r="CU1" t="inlineStr"/>
+      <c r="CV1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>253</v>
+        <v>58316</v>
       </c>
       <c r="B2" t="n">
-        <v>409</v>
+        <v>103495</v>
       </c>
       <c r="C2" t="n">
-        <v>690</v>
+        <v>46464</v>
       </c>
       <c r="D2" t="n">
-        <v>781</v>
+        <v>32540</v>
       </c>
       <c r="E2" t="n">
+        <v>36696</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12217</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50597</v>
+      </c>
+      <c r="H2" t="n">
+        <v>82940</v>
+      </c>
+      <c r="I2" t="n">
+        <v>94776</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30099</v>
+      </c>
+      <c r="K2" t="n">
+        <v>17104</v>
+      </c>
+      <c r="L2" t="n">
+        <v>114775</v>
+      </c>
+      <c r="M2" t="n">
+        <v>92988</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5971</v>
+      </c>
+      <c r="O2" t="n">
+        <v>77107</v>
+      </c>
+      <c r="P2" t="n">
+        <v>40054</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>85364</v>
+      </c>
+      <c r="R2" t="n">
+        <v>84648</v>
+      </c>
+      <c r="S2" t="n">
+        <v>57025</v>
+      </c>
+      <c r="T2" t="n">
+        <v>16856</v>
+      </c>
+      <c r="U2" t="n">
+        <v>100874</v>
+      </c>
+      <c r="V2" t="n">
+        <v>97045</v>
+      </c>
+      <c r="W2" t="n">
+        <v>5207</v>
+      </c>
+      <c r="X2" t="n">
+        <v>128308</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>122748</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>122927</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>75208</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>80222</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>31607</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>23489</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>9492</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>77964</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>1490</v>
-      </c>
-      <c r="G2" t="n">
-        <v>644</v>
-      </c>
-      <c r="H2" t="n">
-        <v>205</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1553</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1121</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1649</v>
-      </c>
-      <c r="L2" t="n">
-        <v>14</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1331</v>
-      </c>
-      <c r="N2" t="n">
-        <v>370</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1021</v>
-      </c>
-      <c r="P2" t="n">
-        <v>312</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>118</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1120</v>
-      </c>
-      <c r="S2" t="n">
-        <v>958</v>
-      </c>
-      <c r="T2" t="n">
-        <v>622</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>20908</v>
-      </c>
-      <c r="B1" t="n">
-        <v>40</v>
-      </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1332</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1173</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1057</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="AH2" t="n">
+        <v>65760</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>107492</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>19805</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>43415</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>933</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>61689</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>54298</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>91619</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>68518</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>53518</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>40919</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>41932</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6699</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>87863</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>81181</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>128802</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>69831</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>24191</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>34129</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>134929</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>134646</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>28174</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>106002</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>48559</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>99143</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>61197</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>109605</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>113943</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>111354</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>87035</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>90724</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>72895</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>110642</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>60415</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>9787</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>117228</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>54326</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4476</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>50273</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>67682</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>13055</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>101652</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>118009</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>45711</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>16158</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>37317</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>96770</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>111065</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>118831</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>26393</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>130663</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>23363</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>84959</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>73907</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>51963</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>22469</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>121262</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>63686</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>119490</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>43721</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>125023</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>126424</v>
+      </c>
+      <c r="CT2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>1754</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1767</v>
-      </c>
-      <c r="H2" t="n">
-        <v>433</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1443</v>
-      </c>
-      <c r="J2" t="n">
-        <v>170</v>
-      </c>
-      <c r="K2" t="n">
-        <v>660</v>
-      </c>
-      <c r="L2" t="n">
-        <v>531</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1595</v>
-      </c>
-      <c r="N2" t="n">
-        <v>316</v>
-      </c>
-      <c r="O2" t="n">
-        <v>955</v>
-      </c>
-      <c r="P2" t="n">
-        <v>959</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>791</v>
-      </c>
-      <c r="R2" t="n">
-        <v>681</v>
-      </c>
-      <c r="S2" t="n">
-        <v>101</v>
-      </c>
-      <c r="T2" t="n">
-        <v>74</v>
+      <c r="CU2" t="n">
+        <v>35420</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>13934</v>
       </c>
     </row>
   </sheetData>

--- a/code/resultados/NWJSSP_OADG_NEH(BestImprovement_LocalSearch).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(BestImprovement_LocalSearch).xlsx
@@ -432,8 +432,12 @@
         <v>314</v>
       </c>
       <c r="B1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -476,104 +480,6 @@
       <c r="B1" t="n">
         <v>29217</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr"/>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr"/>
-      <c r="X1" t="inlineStr"/>
-      <c r="Y1" t="inlineStr"/>
-      <c r="Z1" t="inlineStr"/>
-      <c r="AA1" t="inlineStr"/>
-      <c r="AB1" t="inlineStr"/>
-      <c r="AC1" t="inlineStr"/>
-      <c r="AD1" t="inlineStr"/>
-      <c r="AE1" t="inlineStr"/>
-      <c r="AF1" t="inlineStr"/>
-      <c r="AG1" t="inlineStr"/>
-      <c r="AH1" t="inlineStr"/>
-      <c r="AI1" t="inlineStr"/>
-      <c r="AJ1" t="inlineStr"/>
-      <c r="AK1" t="inlineStr"/>
-      <c r="AL1" t="inlineStr"/>
-      <c r="AM1" t="inlineStr"/>
-      <c r="AN1" t="inlineStr"/>
-      <c r="AO1" t="inlineStr"/>
-      <c r="AP1" t="inlineStr"/>
-      <c r="AQ1" t="inlineStr"/>
-      <c r="AR1" t="inlineStr"/>
-      <c r="AS1" t="inlineStr"/>
-      <c r="AT1" t="inlineStr"/>
-      <c r="AU1" t="inlineStr"/>
-      <c r="AV1" t="inlineStr"/>
-      <c r="AW1" t="inlineStr"/>
-      <c r="AX1" t="inlineStr"/>
-      <c r="AY1" t="inlineStr"/>
-      <c r="AZ1" t="inlineStr"/>
-      <c r="BA1" t="inlineStr"/>
-      <c r="BB1" t="inlineStr"/>
-      <c r="BC1" t="inlineStr"/>
-      <c r="BD1" t="inlineStr"/>
-      <c r="BE1" t="inlineStr"/>
-      <c r="BF1" t="inlineStr"/>
-      <c r="BG1" t="inlineStr"/>
-      <c r="BH1" t="inlineStr"/>
-      <c r="BI1" t="inlineStr"/>
-      <c r="BJ1" t="inlineStr"/>
-      <c r="BK1" t="inlineStr"/>
-      <c r="BL1" t="inlineStr"/>
-      <c r="BM1" t="inlineStr"/>
-      <c r="BN1" t="inlineStr"/>
-      <c r="BO1" t="inlineStr"/>
-      <c r="BP1" t="inlineStr"/>
-      <c r="BQ1" t="inlineStr"/>
-      <c r="BR1" t="inlineStr"/>
-      <c r="BS1" t="inlineStr"/>
-      <c r="BT1" t="inlineStr"/>
-      <c r="BU1" t="inlineStr"/>
-      <c r="BV1" t="inlineStr"/>
-      <c r="BW1" t="inlineStr"/>
-      <c r="BX1" t="inlineStr"/>
-      <c r="BY1" t="inlineStr"/>
-      <c r="BZ1" t="inlineStr"/>
-      <c r="CA1" t="inlineStr"/>
-      <c r="CB1" t="inlineStr"/>
-      <c r="CC1" t="inlineStr"/>
-      <c r="CD1" t="inlineStr"/>
-      <c r="CE1" t="inlineStr"/>
-      <c r="CF1" t="inlineStr"/>
-      <c r="CG1" t="inlineStr"/>
-      <c r="CH1" t="inlineStr"/>
-      <c r="CI1" t="inlineStr"/>
-      <c r="CJ1" t="inlineStr"/>
-      <c r="CK1" t="inlineStr"/>
-      <c r="CL1" t="inlineStr"/>
-      <c r="CM1" t="inlineStr"/>
-      <c r="CN1" t="inlineStr"/>
-      <c r="CO1" t="inlineStr"/>
-      <c r="CP1" t="inlineStr"/>
-      <c r="CQ1" t="inlineStr"/>
-      <c r="CR1" t="inlineStr"/>
-      <c r="CS1" t="inlineStr"/>
-      <c r="CT1" t="inlineStr"/>
-      <c r="CU1" t="inlineStr"/>
-      <c r="CV1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -898,104 +804,6 @@
       <c r="B1" t="n">
         <v>3634086</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr"/>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr"/>
-      <c r="X1" t="inlineStr"/>
-      <c r="Y1" t="inlineStr"/>
-      <c r="Z1" t="inlineStr"/>
-      <c r="AA1" t="inlineStr"/>
-      <c r="AB1" t="inlineStr"/>
-      <c r="AC1" t="inlineStr"/>
-      <c r="AD1" t="inlineStr"/>
-      <c r="AE1" t="inlineStr"/>
-      <c r="AF1" t="inlineStr"/>
-      <c r="AG1" t="inlineStr"/>
-      <c r="AH1" t="inlineStr"/>
-      <c r="AI1" t="inlineStr"/>
-      <c r="AJ1" t="inlineStr"/>
-      <c r="AK1" t="inlineStr"/>
-      <c r="AL1" t="inlineStr"/>
-      <c r="AM1" t="inlineStr"/>
-      <c r="AN1" t="inlineStr"/>
-      <c r="AO1" t="inlineStr"/>
-      <c r="AP1" t="inlineStr"/>
-      <c r="AQ1" t="inlineStr"/>
-      <c r="AR1" t="inlineStr"/>
-      <c r="AS1" t="inlineStr"/>
-      <c r="AT1" t="inlineStr"/>
-      <c r="AU1" t="inlineStr"/>
-      <c r="AV1" t="inlineStr"/>
-      <c r="AW1" t="inlineStr"/>
-      <c r="AX1" t="inlineStr"/>
-      <c r="AY1" t="inlineStr"/>
-      <c r="AZ1" t="inlineStr"/>
-      <c r="BA1" t="inlineStr"/>
-      <c r="BB1" t="inlineStr"/>
-      <c r="BC1" t="inlineStr"/>
-      <c r="BD1" t="inlineStr"/>
-      <c r="BE1" t="inlineStr"/>
-      <c r="BF1" t="inlineStr"/>
-      <c r="BG1" t="inlineStr"/>
-      <c r="BH1" t="inlineStr"/>
-      <c r="BI1" t="inlineStr"/>
-      <c r="BJ1" t="inlineStr"/>
-      <c r="BK1" t="inlineStr"/>
-      <c r="BL1" t="inlineStr"/>
-      <c r="BM1" t="inlineStr"/>
-      <c r="BN1" t="inlineStr"/>
-      <c r="BO1" t="inlineStr"/>
-      <c r="BP1" t="inlineStr"/>
-      <c r="BQ1" t="inlineStr"/>
-      <c r="BR1" t="inlineStr"/>
-      <c r="BS1" t="inlineStr"/>
-      <c r="BT1" t="inlineStr"/>
-      <c r="BU1" t="inlineStr"/>
-      <c r="BV1" t="inlineStr"/>
-      <c r="BW1" t="inlineStr"/>
-      <c r="BX1" t="inlineStr"/>
-      <c r="BY1" t="inlineStr"/>
-      <c r="BZ1" t="inlineStr"/>
-      <c r="CA1" t="inlineStr"/>
-      <c r="CB1" t="inlineStr"/>
-      <c r="CC1" t="inlineStr"/>
-      <c r="CD1" t="inlineStr"/>
-      <c r="CE1" t="inlineStr"/>
-      <c r="CF1" t="inlineStr"/>
-      <c r="CG1" t="inlineStr"/>
-      <c r="CH1" t="inlineStr"/>
-      <c r="CI1" t="inlineStr"/>
-      <c r="CJ1" t="inlineStr"/>
-      <c r="CK1" t="inlineStr"/>
-      <c r="CL1" t="inlineStr"/>
-      <c r="CM1" t="inlineStr"/>
-      <c r="CN1" t="inlineStr"/>
-      <c r="CO1" t="inlineStr"/>
-      <c r="CP1" t="inlineStr"/>
-      <c r="CQ1" t="inlineStr"/>
-      <c r="CR1" t="inlineStr"/>
-      <c r="CS1" t="inlineStr"/>
-      <c r="CT1" t="inlineStr"/>
-      <c r="CU1" t="inlineStr"/>
-      <c r="CV1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1320,104 +1128,6 @@
       <c r="B1" t="n">
         <v>3616924</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr"/>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr"/>
-      <c r="X1" t="inlineStr"/>
-      <c r="Y1" t="inlineStr"/>
-      <c r="Z1" t="inlineStr"/>
-      <c r="AA1" t="inlineStr"/>
-      <c r="AB1" t="inlineStr"/>
-      <c r="AC1" t="inlineStr"/>
-      <c r="AD1" t="inlineStr"/>
-      <c r="AE1" t="inlineStr"/>
-      <c r="AF1" t="inlineStr"/>
-      <c r="AG1" t="inlineStr"/>
-      <c r="AH1" t="inlineStr"/>
-      <c r="AI1" t="inlineStr"/>
-      <c r="AJ1" t="inlineStr"/>
-      <c r="AK1" t="inlineStr"/>
-      <c r="AL1" t="inlineStr"/>
-      <c r="AM1" t="inlineStr"/>
-      <c r="AN1" t="inlineStr"/>
-      <c r="AO1" t="inlineStr"/>
-      <c r="AP1" t="inlineStr"/>
-      <c r="AQ1" t="inlineStr"/>
-      <c r="AR1" t="inlineStr"/>
-      <c r="AS1" t="inlineStr"/>
-      <c r="AT1" t="inlineStr"/>
-      <c r="AU1" t="inlineStr"/>
-      <c r="AV1" t="inlineStr"/>
-      <c r="AW1" t="inlineStr"/>
-      <c r="AX1" t="inlineStr"/>
-      <c r="AY1" t="inlineStr"/>
-      <c r="AZ1" t="inlineStr"/>
-      <c r="BA1" t="inlineStr"/>
-      <c r="BB1" t="inlineStr"/>
-      <c r="BC1" t="inlineStr"/>
-      <c r="BD1" t="inlineStr"/>
-      <c r="BE1" t="inlineStr"/>
-      <c r="BF1" t="inlineStr"/>
-      <c r="BG1" t="inlineStr"/>
-      <c r="BH1" t="inlineStr"/>
-      <c r="BI1" t="inlineStr"/>
-      <c r="BJ1" t="inlineStr"/>
-      <c r="BK1" t="inlineStr"/>
-      <c r="BL1" t="inlineStr"/>
-      <c r="BM1" t="inlineStr"/>
-      <c r="BN1" t="inlineStr"/>
-      <c r="BO1" t="inlineStr"/>
-      <c r="BP1" t="inlineStr"/>
-      <c r="BQ1" t="inlineStr"/>
-      <c r="BR1" t="inlineStr"/>
-      <c r="BS1" t="inlineStr"/>
-      <c r="BT1" t="inlineStr"/>
-      <c r="BU1" t="inlineStr"/>
-      <c r="BV1" t="inlineStr"/>
-      <c r="BW1" t="inlineStr"/>
-      <c r="BX1" t="inlineStr"/>
-      <c r="BY1" t="inlineStr"/>
-      <c r="BZ1" t="inlineStr"/>
-      <c r="CA1" t="inlineStr"/>
-      <c r="CB1" t="inlineStr"/>
-      <c r="CC1" t="inlineStr"/>
-      <c r="CD1" t="inlineStr"/>
-      <c r="CE1" t="inlineStr"/>
-      <c r="CF1" t="inlineStr"/>
-      <c r="CG1" t="inlineStr"/>
-      <c r="CH1" t="inlineStr"/>
-      <c r="CI1" t="inlineStr"/>
-      <c r="CJ1" t="inlineStr"/>
-      <c r="CK1" t="inlineStr"/>
-      <c r="CL1" t="inlineStr"/>
-      <c r="CM1" t="inlineStr"/>
-      <c r="CN1" t="inlineStr"/>
-      <c r="CO1" t="inlineStr"/>
-      <c r="CP1" t="inlineStr"/>
-      <c r="CQ1" t="inlineStr"/>
-      <c r="CR1" t="inlineStr"/>
-      <c r="CS1" t="inlineStr"/>
-      <c r="CT1" t="inlineStr"/>
-      <c r="CU1" t="inlineStr"/>
-      <c r="CV1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1740,8 +1450,12 @@
         <v>324</v>
       </c>
       <c r="B1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2060,14 +1774,6 @@
       <c r="B1" t="n">
         <v>4</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2122,14 +1828,6 @@
       <c r="B1" t="n">
         <v>4</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2184,104 +1882,6 @@
       <c r="B1" t="n">
         <v>18556</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr"/>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr"/>
-      <c r="X1" t="inlineStr"/>
-      <c r="Y1" t="inlineStr"/>
-      <c r="Z1" t="inlineStr"/>
-      <c r="AA1" t="inlineStr"/>
-      <c r="AB1" t="inlineStr"/>
-      <c r="AC1" t="inlineStr"/>
-      <c r="AD1" t="inlineStr"/>
-      <c r="AE1" t="inlineStr"/>
-      <c r="AF1" t="inlineStr"/>
-      <c r="AG1" t="inlineStr"/>
-      <c r="AH1" t="inlineStr"/>
-      <c r="AI1" t="inlineStr"/>
-      <c r="AJ1" t="inlineStr"/>
-      <c r="AK1" t="inlineStr"/>
-      <c r="AL1" t="inlineStr"/>
-      <c r="AM1" t="inlineStr"/>
-      <c r="AN1" t="inlineStr"/>
-      <c r="AO1" t="inlineStr"/>
-      <c r="AP1" t="inlineStr"/>
-      <c r="AQ1" t="inlineStr"/>
-      <c r="AR1" t="inlineStr"/>
-      <c r="AS1" t="inlineStr"/>
-      <c r="AT1" t="inlineStr"/>
-      <c r="AU1" t="inlineStr"/>
-      <c r="AV1" t="inlineStr"/>
-      <c r="AW1" t="inlineStr"/>
-      <c r="AX1" t="inlineStr"/>
-      <c r="AY1" t="inlineStr"/>
-      <c r="AZ1" t="inlineStr"/>
-      <c r="BA1" t="inlineStr"/>
-      <c r="BB1" t="inlineStr"/>
-      <c r="BC1" t="inlineStr"/>
-      <c r="BD1" t="inlineStr"/>
-      <c r="BE1" t="inlineStr"/>
-      <c r="BF1" t="inlineStr"/>
-      <c r="BG1" t="inlineStr"/>
-      <c r="BH1" t="inlineStr"/>
-      <c r="BI1" t="inlineStr"/>
-      <c r="BJ1" t="inlineStr"/>
-      <c r="BK1" t="inlineStr"/>
-      <c r="BL1" t="inlineStr"/>
-      <c r="BM1" t="inlineStr"/>
-      <c r="BN1" t="inlineStr"/>
-      <c r="BO1" t="inlineStr"/>
-      <c r="BP1" t="inlineStr"/>
-      <c r="BQ1" t="inlineStr"/>
-      <c r="BR1" t="inlineStr"/>
-      <c r="BS1" t="inlineStr"/>
-      <c r="BT1" t="inlineStr"/>
-      <c r="BU1" t="inlineStr"/>
-      <c r="BV1" t="inlineStr"/>
-      <c r="BW1" t="inlineStr"/>
-      <c r="BX1" t="inlineStr"/>
-      <c r="BY1" t="inlineStr"/>
-      <c r="BZ1" t="inlineStr"/>
-      <c r="CA1" t="inlineStr"/>
-      <c r="CB1" t="inlineStr"/>
-      <c r="CC1" t="inlineStr"/>
-      <c r="CD1" t="inlineStr"/>
-      <c r="CE1" t="inlineStr"/>
-      <c r="CF1" t="inlineStr"/>
-      <c r="CG1" t="inlineStr"/>
-      <c r="CH1" t="inlineStr"/>
-      <c r="CI1" t="inlineStr"/>
-      <c r="CJ1" t="inlineStr"/>
-      <c r="CK1" t="inlineStr"/>
-      <c r="CL1" t="inlineStr"/>
-      <c r="CM1" t="inlineStr"/>
-      <c r="CN1" t="inlineStr"/>
-      <c r="CO1" t="inlineStr"/>
-      <c r="CP1" t="inlineStr"/>
-      <c r="CQ1" t="inlineStr"/>
-      <c r="CR1" t="inlineStr"/>
-      <c r="CS1" t="inlineStr"/>
-      <c r="CT1" t="inlineStr"/>
-      <c r="CU1" t="inlineStr"/>
-      <c r="CV1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">

--- a/code/resultados/NWJSSP_OADG_NEH(BestImprovement_LocalSearch).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(BestImprovement_LocalSearch).xlsx
@@ -434,10 +434,6 @@
       <c r="B1" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -478,8 +474,106 @@
         <v>6699109</v>
       </c>
       <c r="B1" t="n">
-        <v>29217</v>
-      </c>
+        <v>181856</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
+      <c r="AW1" t="inlineStr"/>
+      <c r="AX1" t="inlineStr"/>
+      <c r="AY1" t="inlineStr"/>
+      <c r="AZ1" t="inlineStr"/>
+      <c r="BA1" t="inlineStr"/>
+      <c r="BB1" t="inlineStr"/>
+      <c r="BC1" t="inlineStr"/>
+      <c r="BD1" t="inlineStr"/>
+      <c r="BE1" t="inlineStr"/>
+      <c r="BF1" t="inlineStr"/>
+      <c r="BG1" t="inlineStr"/>
+      <c r="BH1" t="inlineStr"/>
+      <c r="BI1" t="inlineStr"/>
+      <c r="BJ1" t="inlineStr"/>
+      <c r="BK1" t="inlineStr"/>
+      <c r="BL1" t="inlineStr"/>
+      <c r="BM1" t="inlineStr"/>
+      <c r="BN1" t="inlineStr"/>
+      <c r="BO1" t="inlineStr"/>
+      <c r="BP1" t="inlineStr"/>
+      <c r="BQ1" t="inlineStr"/>
+      <c r="BR1" t="inlineStr"/>
+      <c r="BS1" t="inlineStr"/>
+      <c r="BT1" t="inlineStr"/>
+      <c r="BU1" t="inlineStr"/>
+      <c r="BV1" t="inlineStr"/>
+      <c r="BW1" t="inlineStr"/>
+      <c r="BX1" t="inlineStr"/>
+      <c r="BY1" t="inlineStr"/>
+      <c r="BZ1" t="inlineStr"/>
+      <c r="CA1" t="inlineStr"/>
+      <c r="CB1" t="inlineStr"/>
+      <c r="CC1" t="inlineStr"/>
+      <c r="CD1" t="inlineStr"/>
+      <c r="CE1" t="inlineStr"/>
+      <c r="CF1" t="inlineStr"/>
+      <c r="CG1" t="inlineStr"/>
+      <c r="CH1" t="inlineStr"/>
+      <c r="CI1" t="inlineStr"/>
+      <c r="CJ1" t="inlineStr"/>
+      <c r="CK1" t="inlineStr"/>
+      <c r="CL1" t="inlineStr"/>
+      <c r="CM1" t="inlineStr"/>
+      <c r="CN1" t="inlineStr"/>
+      <c r="CO1" t="inlineStr"/>
+      <c r="CP1" t="inlineStr"/>
+      <c r="CQ1" t="inlineStr"/>
+      <c r="CR1" t="inlineStr"/>
+      <c r="CS1" t="inlineStr"/>
+      <c r="CT1" t="inlineStr"/>
+      <c r="CU1" t="inlineStr"/>
+      <c r="CV1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1452,10 +1546,6 @@
       <c r="B1" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1496,7 +1586,7 @@
         <v>10384</v>
       </c>
       <c r="B1" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
@@ -1550,7 +1640,7 @@
         <v>11834</v>
       </c>
       <c r="B1" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -1604,7 +1694,7 @@
         <v>19770</v>
       </c>
       <c r="B1" t="n">
-        <v>33</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2">
@@ -1688,7 +1778,7 @@
         <v>20908</v>
       </c>
       <c r="B1" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
@@ -1772,7 +1862,7 @@
         <v>119500</v>
       </c>
       <c r="B1" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
@@ -1826,7 +1916,7 @@
         <v>114667</v>
       </c>
       <c r="B1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2">
@@ -1880,7 +1970,7 @@
         <v>6998901</v>
       </c>
       <c r="B1" t="n">
-        <v>18556</v>
+        <v>108895</v>
       </c>
     </row>
     <row r="2">
